--- a/config/auto_configs/2011_Hyundai_Hyundai_Elantra Touring(FD)_G 2.0 MPI.xlsx
+++ b/config/auto_configs/2011_Hyundai_Hyundai_Elantra Touring(FD)_G 2.0 MPI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="NWS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NWS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,6 +539,578 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HMA_0008D</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>P0011</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HMA_0008D</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>P0315</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HMA_0008D</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>P0327</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HMA_0008D</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>P0335</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HMA_0008D</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>P0447</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HMA_0008D</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>P0606</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HMA_0008D</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>P1696</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HMA_0008D</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>P2195</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HMA_0008D</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>P2196</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HMA_0008D</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>P2237</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HMA_0008D</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>P2243</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HMA_0008D</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>P2251</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HMA_0008D</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>P2270</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HMA_0008D</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>P2271</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HMA_0008D</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>P2414</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HMA_0008D</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>P2626</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HMA_0008D</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>U0001</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HMA_0008D</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>U0101</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HMA_00098</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>P0721</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HMA_00098</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>P0722</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HMA_00098</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>P0748</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HMA_00098</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>P0880</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>HMA_00098</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>U0001</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TPMS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HMA_00096</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>HMA_00094</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>IMM</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>HMA_00029</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
